--- a/ig/main/ValueSet-fr-core-schedule-unavailability-reason.xlsx
+++ b/ig/main/ValueSet-fr-core-schedule-unavailability-reason.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T10:51:09+00:00</t>
+    <t>2023-12-11T13:13:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-schedule-unavailability-reason.xlsx
+++ b/ig/main/ValueSet-fr-core-schedule-unavailability-reason.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T13:13:22+00:00</t>
+    <t>2023-12-19T10:49:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-schedule-unavailability-reason.xlsx
+++ b/ig/main/ValueSet-fr-core-schedule-unavailability-reason.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:49:53+00:00</t>
+    <t>2023-12-22T08:30:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-schedule-unavailability-reason.xlsx
+++ b/ig/main/ValueSet-fr-core-schedule-unavailability-reason.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-22T08:30:59+00:00</t>
+    <t>2024-01-19T16:14:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-schedule-unavailability-reason.xlsx
+++ b/ig/main/ValueSet-fr-core-schedule-unavailability-reason.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-19T16:14:08+00:00</t>
+    <t>2024-01-22T11:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-schedule-unavailability-reason.xlsx
+++ b/ig/main/ValueSet-fr-core-schedule-unavailability-reason.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T11:10:15+00:00</t>
+    <t>2024-01-22T11:10:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-schedule-unavailability-reason.xlsx
+++ b/ig/main/ValueSet-fr-core-schedule-unavailability-reason.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T11:10:58+00:00</t>
+    <t>2024-01-29T10:14:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-schedule-unavailability-reason.xlsx
+++ b/ig/main/ValueSet-fr-core-schedule-unavailability-reason.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T10:14:55+00:00</t>
+    <t>2024-01-29T10:26:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-schedule-unavailability-reason.xlsx
+++ b/ig/main/ValueSet-fr-core-schedule-unavailability-reason.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T10:26:27+00:00</t>
+    <t>2024-02-05T10:12:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
